--- a/test/excel/links/written/errors.xlsx
+++ b/test/excel/links/written/errors.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-39313/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-51168/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6542B08-CB60-0F45-BF37-BC18F1CC72D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61D95AC6-430B-154B-96D9-CB1F460E07C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
